--- a/docs/data/current/S_Curve_Dashboard_Source.xlsx
+++ b/docs/data/current/S_Curve_Dashboard_Source.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15 16:27:29</t>
+          <t>2026-05-18 14:52:45</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Do not edit manually. The dashboard regenerates this file from Budget.xlsm and Procurement.xlsx.</t>
+          <t>Do not edit manually. Column F is regenerated dynamically from Procurement.xlsx; column L is the fixed Budget Baseline curve.</t>
         </is>
       </c>
     </row>
@@ -21893,11 +21893,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Budget direct cost</t>
+          <t>Budget Baseline direct cost</t>
         </is>
       </c>
       <c r="K3" s="9" t="n">
-        <v>501457853.0157034</v>
+        <v>499973689.81</v>
       </c>
     </row>
     <row r="5">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>BUDGET / PROGRAMMA CLIENTE</t>
+          <t>BUDGET BASELINE</t>
         </is>
       </c>
     </row>
@@ -21970,12 +21970,12 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Budget_Direct_Monthly</t>
+          <t>Budget_Baseline_Monthly</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Budget_Direct_Cumulative</t>
+          <t>Budget_Baseline_Cumulative</t>
         </is>
       </c>
     </row>
@@ -22087,10 +22087,10 @@
         <v>0.02443990991622114</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>4914057.77</v>
+        <v>7794586.930000001</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>12323042.8</v>
+        <v>15203571.96</v>
       </c>
     </row>
     <row r="10">
@@ -22125,10 +22125,10 @@
         <v>0.03711831387148009</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>6224860.468888889</v>
+        <v>12423640.08</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>18547903.26888889</v>
+        <v>27627212.04</v>
       </c>
     </row>
     <row r="11">
@@ -22163,10 +22163,10 @@
         <v>0.04518114873616575</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>3080461.270952381</v>
+        <v>11336449.17</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>21628364.53984127</v>
+        <v>38963661.21</v>
       </c>
     </row>
     <row r="12">
@@ -22201,10 +22201,10 @@
         <v>0.06538715632285669</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>10298268.19915018</v>
+        <v>13624888.02</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>31926632.73899145</v>
+        <v>52588549.23</v>
       </c>
     </row>
     <row r="13">
@@ -22239,10 +22239,10 @@
         <v>0.1117046013626513</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>24920618.49075124</v>
+        <v>14910518.13</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>56847251.22974269</v>
+        <v>67499067.36</v>
       </c>
     </row>
     <row r="14">
@@ -22277,10 +22277,10 @@
         <v>0.1334627144665459</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>11044595.67496808</v>
+        <v>15028245.62</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>67891846.90471077</v>
+        <v>82527312.98</v>
       </c>
     </row>
     <row r="15">
@@ -22315,10 +22315,10 @@
         <v>0.1581002300042373</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>12651060.24080475</v>
+        <v>24539477.11999999</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>80542907.14551552</v>
+        <v>107066790.1</v>
       </c>
     </row>
     <row r="16">
@@ -22353,10 +22353,10 @@
         <v>0.1903923944644815</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>16840968.47857952</v>
+        <v>31216463.12</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>97383875.62409504</v>
+        <v>138283253.22</v>
       </c>
     </row>
     <row r="17">
@@ -22391,10 +22391,10 @@
         <v>0.2305658315416716</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>21259070.90070589</v>
+        <v>27608192.84999999</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>118642946.5248009</v>
+        <v>165891446.07</v>
       </c>
     </row>
     <row r="18">
@@ -22429,10 +22429,10 @@
         <v>0.2633659042903123</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>17153971.63890617</v>
+        <v>26540967.30000001</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>135796918.1637071</v>
+        <v>192432413.37</v>
       </c>
     </row>
     <row r="19">
@@ -22467,10 +22467,10 @@
         <v>0.3007823385586149</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>19773194.85023951</v>
+        <v>28846792.41</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>155570113.0139466</v>
+        <v>221279205.78</v>
       </c>
     </row>
     <row r="20">
@@ -22505,10 +22505,10 @@
         <v>0.3474162701532711</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>24861930.3932784</v>
+        <v>27022580.63</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>180432043.407225</v>
+        <v>248301786.41</v>
       </c>
     </row>
     <row r="21">
@@ -22543,10 +22543,10 @@
         <v>0.3999162732861552</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>27968549.50484506</v>
+        <v>28325747.31000003</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>208400592.9120701</v>
+        <v>276627533.72</v>
       </c>
     </row>
     <row r="22">
@@ -22581,10 +22581,10 @@
         <v>0.4652333025796565</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>35342841.76083908</v>
+        <v>35039986.07999998</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>243743434.6729091</v>
+        <v>311667519.8</v>
       </c>
     </row>
     <row r="23">
@@ -22619,10 +22619,10 @@
         <v>0.5223508150494413</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>30823036.89110637</v>
+        <v>33822381.40999997</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>274566471.5640155</v>
+        <v>345489901.21</v>
       </c>
     </row>
     <row r="24">
@@ -22657,10 +22657,10 @@
         <v>0.5815730066172758</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>32016185.05832859</v>
+        <v>25897922.24000001</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>306582656.6223441</v>
+        <v>371387823.45</v>
       </c>
     </row>
     <row r="25">
@@ -22695,10 +22695,10 @@
         <v>0.6315572314721892</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>26848740.96685081</v>
+        <v>28095849.06</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>333431397.5891949</v>
+        <v>399483672.51</v>
       </c>
     </row>
     <row r="26">
@@ -22733,10 +22733,10 @@
         <v>0.675171120129185</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>23300575.31623629</v>
+        <v>20736784.01999998</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>356731972.9054312</v>
+        <v>420220456.53</v>
       </c>
     </row>
     <row r="27">
@@ -22771,10 +22771,10 @@
         <v>0.7079923590324528</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>17197990.11634804</v>
+        <v>17315684.93000001</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>373929963.0217792</v>
+        <v>437536141.46</v>
       </c>
     </row>
     <row r="28">
@@ -22809,10 +22809,10 @@
         <v>0.7497670467460185</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>22446419.55108139</v>
+        <v>15763709.59000003</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>396376382.5728606</v>
+        <v>453299851.05</v>
       </c>
     </row>
     <row r="29">
@@ -22847,10 +22847,10 @@
         <v>0.7705321512774643</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>10601806.8521036</v>
+        <v>12623620.61000001</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>406978189.4249642</v>
+        <v>465923471.66</v>
       </c>
     </row>
     <row r="30">
@@ -22885,10 +22885,10 @@
         <v>0.7871021784787184</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>8350089.772514713</v>
+        <v>10976891.06999999</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>415328279.1974789</v>
+        <v>476900362.73</v>
       </c>
     </row>
     <row r="31">
@@ -22923,10 +22923,10 @@
         <v>0.8323721898741486</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>24637776.5005036</v>
+        <v>11889923.66999996</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>439966055.6979825</v>
+        <v>488790286.4</v>
       </c>
     </row>
     <row r="32">
@@ -22961,10 +22961,10 @@
         <v>0.8443972679154598</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>5817816.966203314</v>
+        <v>0</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>445783872.6641858</v>
+        <v>488790286.4</v>
       </c>
     </row>
     <row r="33">
@@ -22999,10 +22999,10 @@
         <v>0.8516214936276489</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>3279069.233192203</v>
+        <v>1910542.100000024</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>449062941.897378</v>
+        <v>490700828.5</v>
       </c>
     </row>
     <row r="34">
@@ -23037,10 +23037,10 @@
         <v>0.8579379403864187</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>2859802.387192203</v>
+        <v>2167008.579999983</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>451922744.2845702</v>
+        <v>492867837.08</v>
       </c>
     </row>
     <row r="35">
@@ -23075,10 +23075,10 @@
         <v>0.8598657878631286</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>308626.9264270753</v>
+        <v>758299.7900000215</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>452231371.2109973</v>
+        <v>493626136.87</v>
       </c>
     </row>
     <row r="36">
@@ -23113,10 +23113,10 @@
         <v>0.8668388712866196</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>3335488.44087152</v>
+        <v>3740876.040000021</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>455566859.6518688</v>
+        <v>497367012.91</v>
       </c>
     </row>
     <row r="37">
@@ -23151,10 +23151,10 @@
         <v>0.8695600385940677</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>966685.0738344828</v>
+        <v>1069040.529999971</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>456533544.7257033</v>
+        <v>498436053.44</v>
       </c>
     </row>
     <row r="38">
@@ -23189,10 +23189,10 @@
         <v>0.9094042395304192</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0</v>
+        <v>454545.4599999785</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>456533544.7257033</v>
+        <v>498890598.9</v>
       </c>
     </row>
     <row r="39">
@@ -23227,10 +23227,10 @@
         <v>0.9101377068352494</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0</v>
+        <v>454545.4500000477</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>456533544.7257033</v>
+        <v>499345144.35</v>
       </c>
     </row>
     <row r="40">
@@ -23265,10 +23265,10 @@
         <v>0.9105577213127656</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>174000</v>
+        <v>628545.4599999785</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>456707544.7257033</v>
+        <v>499973689.81</v>
       </c>
     </row>
     <row r="41">
@@ -23306,7 +23306,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>456707544.7257033</v>
+        <v>499973689.81</v>
       </c>
     </row>
     <row r="42">
@@ -23344,7 +23344,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>456707544.7257033</v>
+        <v>499973689.81</v>
       </c>
     </row>
     <row r="43">
@@ -23379,10 +23379,10 @@
         <v>1</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>44750308.29</v>
+        <v>0</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>501457853.0157033</v>
+        <v>499973689.81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/current/S_Curve_Dashboard_Source.xlsx
+++ b/docs/data/current/S_Curve_Dashboard_Source.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18 14:52:45</t>
+          <t>2026-05-20 11:03:42</t>
         </is>
       </c>
     </row>

--- a/docs/data/current/S_Curve_Dashboard_Source.xlsx
+++ b/docs/data/current/S_Curve_Dashboard_Source.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20 11:03:42</t>
+          <t>2026-05-22 12:53:12</t>
         </is>
       </c>
     </row>

--- a/docs/data/current/S_Curve_Dashboard_Source.xlsx
+++ b/docs/data/current/S_Curve_Dashboard_Source.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-22 12:53:12</t>
+          <t>2026-05-25 16:03:35</t>
         </is>
       </c>
     </row>

--- a/docs/data/current/S_Curve_Dashboard_Source.xlsx
+++ b/docs/data/current/S_Curve_Dashboard_Source.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25 16:03:35</t>
+          <t>2026-05-22 12:53:12</t>
         </is>
       </c>
     </row>

--- a/docs/data/current/S_Curve_Dashboard_Source.xlsx
+++ b/docs/data/current/S_Curve_Dashboard_Source.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 16:42:14</t>
+          <t>2026-06-15 16:47:23</t>
         </is>
       </c>
     </row>
